--- a/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.135.xlsx
+++ b/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.135.xlsx
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -887,7 +887,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.135.xlsx
+++ b/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.135.xlsx
@@ -423,15 +423,15 @@
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
     <col width="60" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="36" customWidth="1" min="6" max="6"/>
     <col width="60" customWidth="1" min="7" max="7"/>
     <col width="60" customWidth="1" min="8" max="8"/>
     <col width="60" customWidth="1" min="9" max="9"/>
-    <col width="60" customWidth="1" min="10" max="10"/>
+    <col width="27" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
     <col width="49" customWidth="1" min="14" max="14"/>
     <col width="60" customWidth="1" min="15" max="15"/>
     <col width="60" customWidth="1" min="16" max="16"/>
@@ -581,12 +581,12 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\preprocessing-tiling_3x1_dp+paddleocr+vl+clean\oocihm.22250\oocihm.22250.135.txt</t>
+          <t>3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\preprocessing-tiling_3x1_dp+paddleocr+vl+clean\oocihm.22250\oocihm.22250.135.txt</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0135.txt</t>
+          <t>3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0135.txt</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr">
@@ -611,21 +611,21 @@
           <t>L76: line starts with digit/letter garbage token | suspicious token(s): 7been (letter/digit mix) | candidate OCR token mismatch vs other OCR: "been" vs "7been" :: 7been to have stated only the names, dates, and amount</t>
         </is>
       </c>
-      <c r="J2" s="1" t="inlineStr">
-        <is>
-          <t>L3: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: comprised, for securing the sum of f â€”â€” and interest;</t>
-        </is>
-      </c>
+      <c r="J2" s="1" t="inlineStr"/>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L13: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Câ€”â€”, and an</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE :: [BOM]ORDERS OF JANUARY 1851.</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE :: [BOM]ORDERS OF JANUARY 1851.</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
-          <t>L19: isolated marker/symbol line :: Â£</t>
+          <t>L19: isolated marker/symbol line :: £</t>
         </is>
       </c>
       <c r="O2" s="1" t="inlineStr">
@@ -646,7 +646,7 @@
       <c r="R2" s="1" t="inlineStr"/>
       <c r="S2" s="1" t="inlineStr">
         <is>
-          <t>L76: line starts with digit/letter garbage token | suspicious token(s): 7been (letter/digit mix) | candidate OCR token mismatch vs other OCR: "been" vs "7been" :: 7been to have stated only the names, dates, and amount</t>
+          <t>L67: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • The names only of the parties are to be set out, not the sub-</t>
         </is>
       </c>
       <c r="T2" s="1" t="inlineStr"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>109</t>
+          <t>92</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr"/>
@@ -682,21 +682,17 @@
           <t>L84: line starts with digit/letter garbage token | suspicious token(s): 1IN (letter/digit mix) :: 1IN CHANCERY.</t>
         </is>
       </c>
-      <c r="J3" s="1" t="inlineStr">
-        <is>
-          <t>L80: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: - day of â€”-</t>
-        </is>
-      </c>
+      <c r="J3" s="1" t="inlineStr"/>
       <c r="K3" s="1" t="inlineStr">
         <is>
-          <t>L26: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢(And fi</t>
+          <t>L26: stray/suspicious non-ASCII glyph(s): U+2022 BULLET :: •(And fi</t>
         </is>
       </c>
       <c r="L3" s="1" t="inlineStr"/>
       <c r="M3" s="1" t="inlineStr"/>
       <c r="N3" s="1" t="inlineStr">
         <is>
-          <t>L20: isolated marker/symbol line :: Â£</t>
+          <t>L20: isolated marker/symbol line :: £</t>
         </is>
       </c>
       <c r="O3" s="1" t="inlineStr">
@@ -713,7 +709,7 @@
       <c r="R3" s="1" t="inlineStr"/>
       <c r="S3" s="1" t="inlineStr">
         <is>
-          <t>L84: line starts with digit/letter garbage token | suspicious token(s): 1IN (letter/digit mix) :: 1IN CHANCERY.</t>
+          <t>L76: line starts with digit/letter garbage token | suspicious token(s): 7been (letter/digit mix) | candidate OCR token mismatch vs other OCR: "been" vs "7been" :: 7been to have stated only the names, dates, and amount</t>
         </is>
       </c>
       <c r="T3" s="1" t="inlineStr"/>
@@ -745,14 +741,10 @@
       <c r="G4" s="1" t="inlineStr"/>
       <c r="H4" s="1" t="inlineStr"/>
       <c r="I4" s="1" t="inlineStr"/>
-      <c r="J4" s="1" t="inlineStr">
-        <is>
-          <t>L88: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: the sum of Â£â€”and interest ; and that C. D., the de-</t>
-        </is>
-      </c>
+      <c r="J4" s="1" t="inlineStr"/>
       <c r="K4" s="1" t="inlineStr">
         <is>
-          <t>L50: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: comprised, for securing the sum of Â£â€” and interest ;</t>
+          <t>L67: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • The names only of the parties are to be set out, not the sub-</t>
         </is>
       </c>
       <c r="L4" s="1" t="inlineStr"/>
@@ -764,17 +756,21 @@
       </c>
       <c r="O4" s="1" t="inlineStr">
         <is>
-          <t>L109: stray/suspicious non-ASCII glyph(s): U+00AC NOT SIGN | isolated marker/symbol line :: â‚¬</t>
+          <t>L109: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: €</t>
         </is>
       </c>
       <c r="P4" s="1" t="inlineStr"/>
       <c r="Q4" s="1" t="inlineStr">
         <is>
-          <t>L94: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: double/multiple hyphen :: â€”,the will of -----------,dated the ----------day of</t>
+          <t>L94: punctuation artifact: double/multiple hyphen :: —,the will of -----------,dated the ----------day of</t>
         </is>
       </c>
       <c r="R4" s="1" t="inlineStr"/>
-      <c r="S4" s="1" t="inlineStr"/>
+      <c r="S4" s="1" t="inlineStr">
+        <is>
+          <t>L84: line starts with digit/letter garbage token | suspicious token(s): 1IN (letter/digit mix) :: 1IN CHANCERY.</t>
+        </is>
+      </c>
       <c r="T4" s="1" t="inlineStr"/>
       <c r="U4" s="1" t="inlineStr"/>
       <c r="V4" s="1" t="inlineStr"/>
@@ -790,12 +786,12 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr"/>
@@ -807,7 +803,7 @@
       <c r="J5" s="1" t="inlineStr"/>
       <c r="K5" s="1" t="inlineStr">
         <is>
-          <t>L56: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: sum of Â£â€” and interest, and the costs of this suit, and</t>
+          <t>L107: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • indenture, dated the day of -</t>
         </is>
       </c>
       <c r="L5" s="1" t="inlineStr"/>
@@ -825,7 +821,11 @@
         </is>
       </c>
       <c r="R5" s="1" t="inlineStr"/>
-      <c r="S5" s="1" t="inlineStr"/>
+      <c r="S5" s="1" t="inlineStr">
+        <is>
+          <t>L107: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • indenture, dated the day of -</t>
+        </is>
+      </c>
       <c r="T5" s="1" t="inlineStr"/>
       <c r="U5" s="1" t="inlineStr"/>
       <c r="V5" s="1" t="inlineStr"/>
@@ -858,7 +858,7 @@
       <c r="J6" s="1" t="inlineStr"/>
       <c r="K6" s="1" t="inlineStr">
         <is>
-          <t>L67: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢ The names only of the parties are to be set out, not the sub-</t>
+          <t>L109: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: €</t>
         </is>
       </c>
       <c r="L6" s="1" t="inlineStr"/>
@@ -872,7 +872,7 @@
       <c r="P6" s="1" t="inlineStr"/>
       <c r="Q6" s="1" t="inlineStr">
         <is>
-          <t>L100: punctuation artifact: double/multiple hyphen :: the sum of Â£-----and interest; and that C. D., the de-</t>
+          <t>L100: punctuation artifact: double/multiple hyphen :: the sum of £-----and interest; and that C. D., the de-</t>
         </is>
       </c>
       <c r="R6" s="1" t="inlineStr"/>
@@ -907,11 +907,7 @@
       <c r="H7" s="1" t="inlineStr"/>
       <c r="I7" s="1" t="inlineStr"/>
       <c r="J7" s="1" t="inlineStr"/>
-      <c r="K7" s="1" t="inlineStr">
-        <is>
-          <t>L91: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: (and the assurances hereinafter mentionedâ€”that is to</t>
-        </is>
-      </c>
+      <c r="K7" s="1" t="inlineStr"/>
       <c r="L7" s="1" t="inlineStr"/>
       <c r="M7" s="1" t="inlineStr"/>
       <c r="N7" s="1" t="inlineStr">
@@ -954,11 +950,7 @@
       <c r="H8" s="1" t="inlineStr"/>
       <c r="I8" s="1" t="inlineStr"/>
       <c r="J8" s="1" t="inlineStr"/>
-      <c r="K8" s="1" t="inlineStr">
-        <is>
-          <t>L94: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: double/multiple hyphen :: â€”,the will of -----------,dated the ----------day of</t>
-        </is>
-      </c>
+      <c r="K8" s="1" t="inlineStr"/>
       <c r="L8" s="1" t="inlineStr"/>
       <c r="M8" s="1" t="inlineStr"/>
       <c r="N8" s="1" t="inlineStr">
@@ -1001,11 +993,7 @@
       <c r="H9" s="1" t="inlineStr"/>
       <c r="I9" s="1" t="inlineStr"/>
       <c r="J9" s="1" t="inlineStr"/>
-      <c r="K9" s="1" t="inlineStr">
-        <is>
-          <t>L107: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢ indenture, dated the day of -</t>
-        </is>
-      </c>
+      <c r="K9" s="1" t="inlineStr"/>
       <c r="L9" s="1" t="inlineStr"/>
       <c r="M9" s="1" t="inlineStr"/>
       <c r="N9" s="1" t="inlineStr"/>
@@ -1029,12 +1017,12 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr"/>
@@ -1044,11 +1032,7 @@
       <c r="H10" s="1" t="inlineStr"/>
       <c r="I10" s="1" t="inlineStr"/>
       <c r="J10" s="1" t="inlineStr"/>
-      <c r="K10" s="1" t="inlineStr">
-        <is>
-          <t>L109: stray/suspicious non-ASCII glyph(s): U+00AC NOT SIGN | isolated marker/symbol line :: â‚¬</t>
-        </is>
-      </c>
+      <c r="K10" s="1" t="inlineStr"/>
       <c r="L10" s="1" t="inlineStr"/>
       <c r="M10" s="1" t="inlineStr"/>
       <c r="N10" s="1" t="inlineStr"/>
@@ -1077,7 +1061,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1194,7 +1178,7 @@
       </c>
       <c r="C14" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D14" s="1" t="inlineStr"/>
